--- a/reports/jobs_2026-09-11.xlsx
+++ b/reports/jobs_2026-09-11.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Compiler Engineer (Machine Learning)</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/Gen-AI-Engineer_SR-45659-1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -563,27 +563,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strategy and Operations Intern </t>
+          <t>Full-Stack Intern - B2B</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -593,12 +593,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/6d849a05-e924-4aef-a6a4-f5e082358517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000148960832</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1078,7 +1078,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1086,12 +1090,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1103,12 +1107,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1121,11 +1125,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1193,17 +1193,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t xml:space="preserve">IT B2B/EDI Developer </t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1211,7 +1211,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1219,12 +1223,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000148716589</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1236,17 +1240,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT B2B/EDI Developer </t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1266,12 +1270,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000148716589</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1283,17 +1287,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1313,12 +1317,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1360,7 +1364,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1382,7 +1386,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1407,7 +1411,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1424,17 +1428,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1442,11 +1446,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer_SR-43347</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer- WD</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer_SR-43347</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1514,17 +1514,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer- WD</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1532,7 +1532,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Chennai, in</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1540,12 +1544,12 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1557,17 +1561,17 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1583,12 +1587,12 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/London/Snowflake-Data-Engineer_SR-45644</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1600,17 +1604,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Python Backend Engineer</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1626,12 +1630,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/Data-Engineer-Business-Intelligence-Senior-Consultant-Architect-6_SR-43710-1</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1643,17 +1647,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1661,11 +1665,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, in</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1690,17 +1690,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1708,7 +1708,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1716,12 +1720,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1733,12 +1737,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1751,7 +1755,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1759,12 +1767,12 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1776,12 +1784,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1794,7 +1802,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1802,12 +1814,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1819,17 +1831,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1839,7 +1851,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1849,12 +1861,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1866,17 +1878,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1886,7 +1898,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1896,12 +1908,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1913,17 +1925,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1931,11 +1943,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1943,12 +1951,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1960,12 +1968,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1978,11 +1986,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1990,12 +1994,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2007,17 +2011,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2027,7 +2031,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2037,12 +2041,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2054,17 +2058,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2080,12 +2084,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2097,12 +2101,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2115,7 +2119,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2123,12 +2131,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2140,12 +2148,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2160,7 +2168,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2170,12 +2178,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7922676</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2187,12 +2195,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2205,7 +2213,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2213,12 +2225,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2230,17 +2242,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2248,11 +2260,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2260,12 +2268,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2277,27 +2285,27 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>SRE Operations Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2307,12 +2315,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2324,17 +2332,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2350,12 +2358,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2367,27 +2375,27 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SRE Operations Engineer</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2397,12 +2405,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2414,12 +2422,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2432,7 +2440,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2440,12 +2452,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2462,7 +2474,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2477,7 +2489,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2487,7 +2499,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2509,7 +2521,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2519,7 +2531,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -2534,7 +2546,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2556,7 +2568,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2581,7 +2593,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2603,7 +2615,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2613,12 +2625,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2628,7 +2640,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2650,7 +2662,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2665,7 +2677,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2675,7 +2687,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2692,17 +2704,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2710,11 +2722,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2722,12 +2730,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2739,17 +2747,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2759,7 +2767,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2769,12 +2777,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2786,12 +2794,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2804,7 +2812,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2812,12 +2824,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2834,7 +2846,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2859,7 +2871,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2876,17 +2888,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2894,11 +2906,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2906,12 +2914,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2923,17 +2931,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2943,7 +2951,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2953,12 +2961,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2970,12 +2978,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2988,7 +2996,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -2996,12 +3008,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3013,17 +3025,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3033,7 +3045,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3043,12 +3055,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3065,12 +3077,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3080,7 +3092,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3090,7 +3102,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3112,7 +3124,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3137,7 +3149,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3154,27 +3166,27 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t xml:space="preserve">Strategy and Operations Intern </t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3184,12 +3196,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://jobs.ashbyhq.com/sarvam/6d849a05-e924-4aef-a6a4-f5e082358517</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3201,17 +3213,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3221,7 +3233,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3231,12 +3243,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3248,17 +3260,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3266,11 +3278,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -3278,12 +3286,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3300,7 +3308,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>Creative Producer - AI</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3321,7 +3329,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3338,17 +3346,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Creative Producer - AI</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3356,7 +3364,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -3364,12 +3376,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3386,12 +3398,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3411,7 +3423,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3428,17 +3440,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3448,7 +3460,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>CO-Colombia-Remote</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3458,12 +3470,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3475,17 +3487,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3493,11 +3505,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>CO-Colombia-Remote</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -3505,12 +3513,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3522,12 +3530,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3540,7 +3548,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -3548,12 +3560,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3565,17 +3577,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3585,7 +3597,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3595,12 +3607,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3617,12 +3629,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3642,7 +3654,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3656,55 +3668,8 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I71"/>
+  <autoFilter ref="A1:I70"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -3775,7 +3740,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3787,7 +3751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3815,17 +3779,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>playwright failed: Page.content: Unable to retrieve content because the page is navigating and changing the content.</t>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://exotel.com/careers/", waiting until "networkidle"
+</t>
         </is>
       </c>
     </row>
@@ -3852,35 +3819,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Log9 Materials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://exotel.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Log9 Materials</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.log9materials.com/careers</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3889,18 +3836,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3909,18 +3856,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Vymo</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://getvymo.com/careers/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3929,18 +3876,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3949,38 +3896,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3989,18 +3916,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Darwinbox</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://darwinbox.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4009,18 +3936,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4029,18 +3956,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4049,18 +3976,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4069,6 +3996,46 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OYO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.oyorooms.com/careers/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -4092,35 +4059,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shiprocket</t>
+          <t>Coforge</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.shiprocket.in/careers/</t>
+          <t>https://www.coforge.com/careers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Coforge</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://www.coforge.com/careers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4129,18 +4076,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4149,18 +4096,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
